--- a/pds_admin_Punjab_R/Backend/Backend/WB_Selected_Routes.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/WB_Selected_Routes.xlsx
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -426,54 +426,54 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>1046</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>625</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>522</v>
+        <v>393</v>
       </c>
       <c r="D2">
-        <v>31.4204409</v>
+        <v>31.863261</v>
       </c>
       <c r="E2">
-        <v>75.69994199999999</v>
+        <v>74.945286</v>
       </c>
       <c r="F2">
-        <v>1.94</v>
+        <v>3.78</v>
       </c>
       <c r="G2">
-        <v>1.86</v>
+        <v>3.01</v>
       </c>
       <c r="H2">
-        <v>3.8</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="B3">
-        <v>396</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>280</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>30.154922</v>
+        <v>31.781936</v>
       </c>
       <c r="E3">
-        <v>74.193507</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="F3">
-        <v>0.28</v>
+        <v>15.86</v>
       </c>
       <c r="G3">
-        <v>1.18</v>
+        <v>17.05</v>
       </c>
       <c r="H3">
-        <v>1.46</v>
+        <v>32.91</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -481,25 +481,25 @@
         <v>501</v>
       </c>
       <c r="B4">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C4">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D4">
-        <v>30.15894356</v>
+        <v>30.154922</v>
       </c>
       <c r="E4">
-        <v>74.18094151</v>
+        <v>74.193507</v>
       </c>
       <c r="F4">
-        <v>1.44</v>
+        <v>0.28</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="H4">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -507,7 +507,7 @@
         <v>501</v>
       </c>
       <c r="B5">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C5">
         <v>286</v>
@@ -522,10 +522,10 @@
         <v>1.44</v>
       </c>
       <c r="G5">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -533,7 +533,7 @@
         <v>501</v>
       </c>
       <c r="B6">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C6">
         <v>286</v>
@@ -548,10 +548,10 @@
         <v>1.44</v>
       </c>
       <c r="G6">
-        <v>1.63</v>
+        <v>0.05</v>
       </c>
       <c r="H6">
-        <v>3.07</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -559,25 +559,25 @@
         <v>501</v>
       </c>
       <c r="B7">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D7">
-        <v>30.163017</v>
+        <v>30.15894356</v>
       </c>
       <c r="E7">
-        <v>74.186234</v>
+        <v>74.18094151</v>
       </c>
       <c r="F7">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="G7">
-        <v>0.72</v>
+        <v>1.63</v>
       </c>
       <c r="H7">
-        <v>1.87</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -608,7 +608,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B9">
         <v>407</v>
@@ -623,117 +623,117 @@
         <v>74.161942</v>
       </c>
       <c r="F9">
-        <v>18.11</v>
+        <v>4.63</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>18.11</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B10">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C10">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D10">
-        <v>30.105887</v>
+        <v>30.090357</v>
       </c>
       <c r="E10">
-        <v>74.18092900000001</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="F10">
-        <v>8.73</v>
+        <v>13.42</v>
       </c>
       <c r="G10">
-        <v>0.09</v>
+        <v>0.27</v>
       </c>
       <c r="H10">
-        <v>8.81</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B11">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C11">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D11">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="E11">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="F11">
-        <v>11.44</v>
+        <v>13.55</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="H11">
-        <v>11.44</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B12">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C12">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D12">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="E12">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="F12">
-        <v>16.9</v>
+        <v>8.73</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="H12">
-        <v>16.9</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B13">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C13">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D13">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="E13">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="F13">
-        <v>9.460000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="G13">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>10.17</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -741,25 +741,25 @@
         <v>506</v>
       </c>
       <c r="B14">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C14">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D14">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="E14">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="F14">
-        <v>9.460000000000001</v>
+        <v>12.68</v>
       </c>
       <c r="G14">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>10.31</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -767,7 +767,7 @@
         <v>507</v>
       </c>
       <c r="B15">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C15">
         <v>281</v>
@@ -782,67 +782,67 @@
         <v>6.68</v>
       </c>
       <c r="G15">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="H15">
-        <v>7.08</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B16">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="C16">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D16">
-        <v>30.163017</v>
+        <v>30.090357</v>
       </c>
       <c r="E16">
-        <v>74.186234</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="F16">
-        <v>13.62</v>
+        <v>6.68</v>
       </c>
       <c r="G16">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="H16">
-        <v>14.47</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B17">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C17">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D17">
-        <v>30.180346</v>
+        <v>30.163017</v>
       </c>
       <c r="E17">
-        <v>74.17439299999999</v>
+        <v>74.186234</v>
       </c>
       <c r="F17">
-        <v>6.68</v>
+        <v>13.62</v>
       </c>
       <c r="G17">
-        <v>2.67</v>
+        <v>0.72</v>
       </c>
       <c r="H17">
-        <v>9.34</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B18">
         <v>407</v>
@@ -857,281 +857,281 @@
         <v>74.161942</v>
       </c>
       <c r="F18">
-        <v>16.65</v>
+        <v>16.95</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>16.65</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B19">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C19">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D19">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="E19">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F19">
-        <v>16.06</v>
+        <v>6.68</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H19">
-        <v>16.06</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B20">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C20">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D20">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="E20">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="F20">
-        <v>9.07</v>
+        <v>16.65</v>
       </c>
       <c r="G20">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>9.67</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B21">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C21">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D21">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="E21">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="F21">
-        <v>16.24</v>
+        <v>12.02</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="H21">
-        <v>16.24</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B22">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C22">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D22">
-        <v>30.105887</v>
+        <v>30.175344</v>
       </c>
       <c r="E22">
-        <v>74.18092900000001</v>
+        <v>74.178363</v>
       </c>
       <c r="F22">
-        <v>16.59</v>
+        <v>9.07</v>
       </c>
       <c r="G22">
-        <v>0.09</v>
+        <v>0.6</v>
       </c>
       <c r="H22">
-        <v>16.68</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B23">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C23">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D23">
-        <v>30.100105</v>
+        <v>30.126927</v>
       </c>
       <c r="E23">
-        <v>74.20670699999999</v>
+        <v>74.161942</v>
       </c>
       <c r="F23">
-        <v>8.130000000000001</v>
+        <v>16.24</v>
       </c>
       <c r="G23">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>8.43</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B24">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="C24">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D24">
-        <v>30.126927</v>
+        <v>30.090357</v>
       </c>
       <c r="E24">
-        <v>74.161942</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="F24">
-        <v>13.16</v>
+        <v>14.48</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H24">
-        <v>13.16</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B25">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C25">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D25">
-        <v>30.175344</v>
+        <v>30.090357</v>
       </c>
       <c r="E25">
-        <v>74.178363</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="F25">
-        <v>17.41</v>
+        <v>7.77</v>
       </c>
       <c r="G25">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
       <c r="H25">
-        <v>18.02</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B26">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C26">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D26">
-        <v>30.163017</v>
+        <v>30.180346</v>
       </c>
       <c r="E26">
-        <v>74.186234</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F26">
-        <v>17.16</v>
+        <v>9.56</v>
       </c>
       <c r="G26">
-        <v>0.85</v>
+        <v>2.67</v>
       </c>
       <c r="H26">
-        <v>18.02</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B27">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C27">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D27">
-        <v>30.180346</v>
+        <v>30.163017</v>
       </c>
       <c r="E27">
-        <v>74.17439299999999</v>
+        <v>74.186234</v>
       </c>
       <c r="F27">
-        <v>9.56</v>
+        <v>6.29</v>
       </c>
       <c r="G27">
-        <v>2.67</v>
+        <v>0.72</v>
       </c>
       <c r="H27">
-        <v>12.22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B28">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C28">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D28">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="E28">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="F28">
-        <v>6.29</v>
+        <v>16.12</v>
       </c>
       <c r="G28">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>7.14</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B29">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C29">
         <v>285</v>
@@ -1143,278 +1143,278 @@
         <v>74.17439299999999</v>
       </c>
       <c r="F29">
-        <v>14.76</v>
+        <v>8.69</v>
       </c>
       <c r="G29">
-        <v>2.67</v>
+        <v>0.4</v>
       </c>
       <c r="H29">
-        <v>17.43</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B30">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C30">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D30">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="E30">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="F30">
-        <v>16.12</v>
+        <v>12.17</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="H30">
-        <v>16.12</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B31">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C31">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D31">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="E31">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="F31">
-        <v>9.199999999999999</v>
+        <v>13.74</v>
       </c>
       <c r="G31">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>9.81</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B32">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C32">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D32">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="E32">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="F32">
-        <v>8.69</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G32">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>9.09</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B33">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="C33">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D33">
-        <v>30.126927</v>
+        <v>30.090357</v>
       </c>
       <c r="E33">
-        <v>74.161942</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="F33">
-        <v>13.74</v>
+        <v>13.91</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H33">
-        <v>13.74</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B34">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C34">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D34">
-        <v>30.126927</v>
+        <v>30.163017</v>
       </c>
       <c r="E34">
-        <v>74.161942</v>
+        <v>74.186234</v>
       </c>
       <c r="F34">
-        <v>22.2</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="H34">
-        <v>22.2</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B35">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="C35">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D35">
-        <v>30.090357</v>
+        <v>30.175344</v>
       </c>
       <c r="E35">
-        <v>74.20853700000001</v>
+        <v>74.178363</v>
       </c>
       <c r="F35">
-        <v>23.25</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G35">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H35">
-        <v>24.06</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B36">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C36">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D36">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="E36">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="F36">
-        <v>9.449999999999999</v>
+        <v>13.64</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="H36">
-        <v>9.449999999999999</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B37">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="C37">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D37">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="E37">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="F37">
-        <v>13.91</v>
+        <v>17.47</v>
       </c>
       <c r="G37">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>14.19</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B38">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="C38">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D38">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="E38">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="F38">
-        <v>13.91</v>
+        <v>18.37</v>
       </c>
       <c r="G38">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>14.31</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B39">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C39">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D39">
-        <v>30.175344</v>
+        <v>30.180346</v>
       </c>
       <c r="E39">
-        <v>74.178363</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F39">
-        <v>9.880000000000001</v>
+        <v>6.95</v>
       </c>
       <c r="G39">
-        <v>0.6</v>
+        <v>2.67</v>
       </c>
       <c r="H39">
-        <v>10.48</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B40">
         <v>407</v>
@@ -1429,18 +1429,18 @@
         <v>74.161942</v>
       </c>
       <c r="F40">
-        <v>17.47</v>
+        <v>10.93</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>17.47</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B41">
         <v>407</v>
@@ -1455,70 +1455,70 @@
         <v>74.161942</v>
       </c>
       <c r="F41">
-        <v>18.37</v>
+        <v>13.39</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>18.37</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B42">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="C42">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D42">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="E42">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="F42">
-        <v>19.1</v>
+        <v>11.24</v>
       </c>
       <c r="G42">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>19.38</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B43">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C43">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D43">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="E43">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="F43">
-        <v>6.95</v>
+        <v>5.65</v>
       </c>
       <c r="G43">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>9.619999999999999</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="B44">
         <v>407</v>
@@ -1533,174 +1533,174 @@
         <v>74.161942</v>
       </c>
       <c r="F44">
-        <v>10.93</v>
+        <v>13.52</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>10.93</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="B45">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C45">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D45">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="E45">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="F45">
-        <v>13.39</v>
+        <v>13.62</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="H45">
-        <v>13.39</v>
+        <v>13.71</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B46">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C46">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D46">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="E46">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F46">
-        <v>11.24</v>
+        <v>9.44</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H46">
-        <v>11.24</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B47">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C47">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D47">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="E47">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F47">
-        <v>5.65</v>
+        <v>8.66</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H47">
-        <v>5.65</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B48">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C48">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D48">
-        <v>30.090357</v>
+        <v>30.180346</v>
       </c>
       <c r="E48">
-        <v>74.20853700000001</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F48">
-        <v>16.79</v>
+        <v>9.58</v>
       </c>
       <c r="G48">
-        <v>0.27</v>
+        <v>2.67</v>
       </c>
       <c r="H48">
-        <v>17.06</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="B49">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C49">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D49">
-        <v>30.090357</v>
+        <v>30.105887</v>
       </c>
       <c r="E49">
-        <v>74.20853700000001</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="F49">
-        <v>16.79</v>
+        <v>14.61</v>
       </c>
       <c r="G49">
-        <v>0.8100000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H49">
-        <v>17.6</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="B50">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="C50">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D50">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="E50">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="F50">
-        <v>22.65</v>
+        <v>4.23</v>
       </c>
       <c r="G50">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>22.93</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B51">
         <v>407</v>
@@ -1715,18 +1715,18 @@
         <v>74.161942</v>
       </c>
       <c r="F51">
-        <v>13.52</v>
+        <v>17.22</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>13.52</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B52">
         <v>407</v>
@@ -1741,44 +1741,44 @@
         <v>74.161942</v>
       </c>
       <c r="F52">
-        <v>15.98</v>
+        <v>16.25</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>15.98</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="B53">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C53">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D53">
-        <v>30.180346</v>
+        <v>30.175344</v>
       </c>
       <c r="E53">
-        <v>74.17439299999999</v>
+        <v>74.178363</v>
       </c>
       <c r="F53">
-        <v>9.44</v>
+        <v>15.77</v>
       </c>
       <c r="G53">
-        <v>2.67</v>
+        <v>0.6</v>
       </c>
       <c r="H53">
-        <v>12.11</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B54">
         <v>400</v>
@@ -1793,21 +1793,21 @@
         <v>74.17439299999999</v>
       </c>
       <c r="F54">
-        <v>8.66</v>
+        <v>11.65</v>
       </c>
       <c r="G54">
         <v>2.67</v>
       </c>
       <c r="H54">
-        <v>11.33</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B55">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C55">
         <v>285</v>
@@ -1819,96 +1819,96 @@
         <v>74.17439299999999</v>
       </c>
       <c r="F55">
-        <v>9.58</v>
+        <v>11.65</v>
       </c>
       <c r="G55">
-        <v>2.67</v>
+        <v>0.4</v>
       </c>
       <c r="H55">
-        <v>12.25</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B56">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C56">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D56">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="E56">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="F56">
-        <v>16.86</v>
+        <v>12.91</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H56">
-        <v>16.86</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B57">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C57">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D57">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="E57">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="F57">
-        <v>4.23</v>
+        <v>13.44</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H57">
-        <v>4.23</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="B58">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C58">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D58">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="E58">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F58">
-        <v>17.22</v>
+        <v>17.49</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H58">
-        <v>17.22</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B59">
         <v>400</v>
@@ -1923,18 +1923,18 @@
         <v>74.17439299999999</v>
       </c>
       <c r="F59">
-        <v>14.86</v>
+        <v>15.83</v>
       </c>
       <c r="G59">
         <v>2.67</v>
       </c>
       <c r="H59">
-        <v>17.53</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>549</v>
+        <v>612</v>
       </c>
       <c r="B60">
         <v>401</v>
@@ -1949,767 +1949,637 @@
         <v>74.178363</v>
       </c>
       <c r="F60">
-        <v>15.77</v>
+        <v>15.13</v>
       </c>
       <c r="G60">
         <v>0.6</v>
       </c>
       <c r="H60">
-        <v>16.37</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>550</v>
+        <v>1046</v>
       </c>
       <c r="B61">
-        <v>402</v>
+        <v>625</v>
       </c>
       <c r="C61">
-        <v>285</v>
+        <v>522</v>
       </c>
       <c r="D61">
-        <v>30.180346</v>
+        <v>31.4204409</v>
       </c>
       <c r="E61">
-        <v>74.17439299999999</v>
+        <v>75.69994199999999</v>
       </c>
       <c r="F61">
-        <v>11.65</v>
+        <v>1.94</v>
       </c>
       <c r="G61">
-        <v>0.4</v>
+        <v>1.86</v>
       </c>
       <c r="H61">
-        <v>12.06</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>551</v>
+        <v>1577</v>
       </c>
       <c r="B62">
-        <v>401</v>
+        <v>866</v>
       </c>
       <c r="C62">
-        <v>279</v>
+        <v>1455</v>
       </c>
       <c r="D62">
-        <v>30.175344</v>
+        <v>30.450458</v>
       </c>
       <c r="E62">
-        <v>74.178363</v>
+        <v>74.489422</v>
       </c>
       <c r="F62">
-        <v>12.91</v>
+        <v>7.65</v>
       </c>
       <c r="G62">
-        <v>0.6</v>
+        <v>3.55</v>
       </c>
       <c r="H62">
-        <v>13.51</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>552</v>
+        <v>1577</v>
       </c>
       <c r="B63">
-        <v>401</v>
+        <v>870</v>
       </c>
       <c r="C63">
-        <v>279</v>
+        <v>1455</v>
       </c>
       <c r="D63">
-        <v>30.175344</v>
+        <v>30.450458</v>
       </c>
       <c r="E63">
-        <v>74.178363</v>
+        <v>74.489422</v>
       </c>
       <c r="F63">
-        <v>13.44</v>
+        <v>7.65</v>
       </c>
       <c r="G63">
-        <v>0.6</v>
+        <v>3.55</v>
       </c>
       <c r="H63">
-        <v>14.04</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>1322</v>
+        <v>1577</v>
       </c>
       <c r="B64">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="C64">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="D64">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="E64">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="F64">
-        <v>39.4</v>
+        <v>7.65</v>
       </c>
       <c r="G64">
-        <v>95.73</v>
+        <v>3.55</v>
       </c>
       <c r="H64">
-        <v>135.13</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>1322</v>
+        <v>1577</v>
       </c>
       <c r="B65">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="C65">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="D65">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="E65">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="F65">
-        <v>39.4</v>
+        <v>7.65</v>
       </c>
       <c r="G65">
-        <v>95.73</v>
+        <v>3.55</v>
       </c>
       <c r="H65">
-        <v>135.13</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="B66">
         <v>866</v>
       </c>
       <c r="C66">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="D66">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="E66">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="F66">
-        <v>39.4</v>
+        <v>5.62</v>
       </c>
       <c r="G66">
-        <v>95.73</v>
+        <v>3.55</v>
       </c>
       <c r="H66">
-        <v>135.13</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="B67">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C67">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="D67">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="E67">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="F67">
-        <v>39.4</v>
+        <v>5.62</v>
       </c>
       <c r="G67">
-        <v>95.73</v>
+        <v>3.55</v>
       </c>
       <c r="H67">
-        <v>135.13</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="B68">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="C68">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="D68">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="E68">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="F68">
-        <v>39.4</v>
+        <v>5.62</v>
       </c>
       <c r="G68">
-        <v>95.73</v>
+        <v>3.55</v>
       </c>
       <c r="H68">
-        <v>135.13</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="B69">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="C69">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="D69">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="E69">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="F69">
-        <v>39.4</v>
+        <v>0.21</v>
       </c>
       <c r="G69">
-        <v>95.73</v>
+        <v>4.99</v>
       </c>
       <c r="H69">
-        <v>135.13</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="B70">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="C70">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="D70">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="E70">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="F70">
-        <v>39.4</v>
+        <v>0.21</v>
       </c>
       <c r="G70">
-        <v>95.73</v>
+        <v>4.99</v>
       </c>
       <c r="H70">
-        <v>135.13</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="B71">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="C71">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="D71">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="E71">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="F71">
-        <v>39.4</v>
+        <v>0.21</v>
       </c>
       <c r="G71">
-        <v>95.73</v>
+        <v>4.99</v>
       </c>
       <c r="H71">
-        <v>135.13</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="B72">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="C72">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="D72">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="E72">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="F72">
-        <v>39.4</v>
+        <v>0.21</v>
       </c>
       <c r="G72">
-        <v>95.73</v>
+        <v>4.99</v>
       </c>
       <c r="H72">
-        <v>135.13</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="B73">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="C73">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="D73">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="E73">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="F73">
-        <v>39.4</v>
+        <v>0.21</v>
       </c>
       <c r="G73">
-        <v>95.73</v>
+        <v>4.99</v>
       </c>
       <c r="H73">
-        <v>135.13</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="B74">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C74">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="D74">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="E74">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="F74">
-        <v>47.15</v>
+        <v>0.21</v>
       </c>
       <c r="G74">
-        <v>86.84999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="H74">
-        <v>134</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="B75">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C75">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="D75">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="E75">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="F75">
-        <v>47.15</v>
+        <v>0.21</v>
       </c>
       <c r="G75">
-        <v>86.84999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="H75">
-        <v>134</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="B76">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C76">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="D76">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="E76">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="F76">
-        <v>47.15</v>
+        <v>0.21</v>
       </c>
       <c r="G76">
-        <v>86.84999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="H76">
-        <v>134</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="B77">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C77">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="D77">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="E77">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="F77">
-        <v>47.15</v>
+        <v>0.21</v>
       </c>
       <c r="G77">
-        <v>86.84999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="H77">
-        <v>134</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="B78">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C78">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="D78">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="E78">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="F78">
-        <v>47.15</v>
+        <v>0.21</v>
       </c>
       <c r="G78">
-        <v>86.84999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="H78">
-        <v>134</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>1324</v>
+        <v>1607</v>
       </c>
       <c r="B79">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="C79">
-        <v>216</v>
+        <v>1512</v>
       </c>
       <c r="D79">
-        <v>30.5076194</v>
+        <v>30.4713293</v>
       </c>
       <c r="E79">
-        <v>74.958715</v>
+        <v>74.5033904</v>
       </c>
       <c r="F79">
-        <v>80.06999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="G79">
-        <v>48.72</v>
+        <v>4.99</v>
       </c>
       <c r="H79">
-        <v>128.79</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>1325</v>
+        <v>1607</v>
       </c>
       <c r="B80">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="C80">
-        <v>217</v>
+        <v>1512</v>
       </c>
       <c r="D80">
-        <v>30.51445</v>
+        <v>30.4713293</v>
       </c>
       <c r="E80">
-        <v>74.89836</v>
+        <v>74.5033904</v>
       </c>
       <c r="F80">
-        <v>88.04000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="G80">
-        <v>43.08</v>
+        <v>4.99</v>
       </c>
       <c r="H80">
-        <v>131.12</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>1326</v>
+        <v>1660</v>
       </c>
       <c r="B81">
-        <v>866</v>
+        <v>401</v>
       </c>
       <c r="C81">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c r="D81">
-        <v>30.58822</v>
+        <v>30.175344</v>
       </c>
       <c r="E81">
-        <v>75.6722</v>
+        <v>74.178363</v>
       </c>
       <c r="F81">
-        <v>19.56</v>
+        <v>13.33</v>
       </c>
       <c r="G81">
-        <v>117.62</v>
+        <v>0.6</v>
       </c>
       <c r="H81">
-        <v>137.19</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>1326</v>
+        <v>1660</v>
       </c>
       <c r="B82">
-        <v>874</v>
+        <v>406</v>
       </c>
       <c r="C82">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c r="D82">
-        <v>30.58822</v>
+        <v>30.175344</v>
       </c>
       <c r="E82">
-        <v>75.6722</v>
+        <v>74.178363</v>
       </c>
       <c r="F82">
-        <v>19.56</v>
+        <v>13.33</v>
       </c>
       <c r="G82">
-        <v>117.62</v>
+        <v>0.71</v>
       </c>
       <c r="H82">
-        <v>137.19</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>1326</v>
+        <v>2153</v>
       </c>
       <c r="B83">
-        <v>879</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>57</v>
+        <v>1948</v>
       </c>
       <c r="D83">
-        <v>30.58822</v>
+        <v>31.361236</v>
       </c>
       <c r="E83">
-        <v>75.6722</v>
+        <v>74.66727400000001</v>
       </c>
       <c r="F83">
-        <v>19.56</v>
+        <v>5.71</v>
       </c>
       <c r="G83">
-        <v>117.62</v>
+        <v>21.72</v>
       </c>
       <c r="H83">
-        <v>137.19</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
-        <v>1327</v>
+        <v>2153</v>
       </c>
       <c r="B84">
-        <v>866</v>
+        <v>4</v>
       </c>
       <c r="C84">
-        <v>217</v>
+        <v>1948</v>
       </c>
       <c r="D84">
-        <v>30.51445</v>
+        <v>31.361236</v>
       </c>
       <c r="E84">
-        <v>74.89836</v>
+        <v>74.66727400000001</v>
       </c>
       <c r="F84">
-        <v>82.51000000000001</v>
+        <v>5.71</v>
       </c>
       <c r="G84">
-        <v>43.08</v>
+        <v>21.72</v>
       </c>
       <c r="H84">
-        <v>125.59</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85">
-        <v>1328</v>
-      </c>
-      <c r="B85">
-        <v>866</v>
-      </c>
-      <c r="C85">
-        <v>216</v>
-      </c>
-      <c r="D85">
-        <v>30.5076194</v>
-      </c>
-      <c r="E85">
-        <v>74.958715</v>
-      </c>
-      <c r="F85">
-        <v>82.76000000000001</v>
-      </c>
-      <c r="G85">
-        <v>48.72</v>
-      </c>
-      <c r="H85">
-        <v>131.47</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86">
-        <v>1328</v>
-      </c>
-      <c r="B86">
-        <v>880</v>
-      </c>
-      <c r="C86">
-        <v>216</v>
-      </c>
-      <c r="D86">
-        <v>30.5076194</v>
-      </c>
-      <c r="E86">
-        <v>74.958715</v>
-      </c>
-      <c r="F86">
-        <v>82.76000000000001</v>
-      </c>
-      <c r="G86">
-        <v>48.72</v>
-      </c>
-      <c r="H86">
-        <v>131.47</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87">
-        <v>1329</v>
-      </c>
-      <c r="B87">
-        <v>877</v>
-      </c>
-      <c r="C87">
-        <v>678</v>
-      </c>
-      <c r="D87">
-        <v>30.633572</v>
-      </c>
-      <c r="E87">
-        <v>75.628421</v>
-      </c>
-      <c r="F87">
-        <v>24.17</v>
-      </c>
-      <c r="G87">
-        <v>114.19</v>
-      </c>
-      <c r="H87">
-        <v>138.36</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88">
-        <v>1330</v>
-      </c>
-      <c r="B88">
-        <v>872</v>
-      </c>
-      <c r="C88">
-        <v>1225</v>
-      </c>
-      <c r="D88">
-        <v>30.5792101</v>
-      </c>
-      <c r="E88">
-        <v>75.30097960000001</v>
-      </c>
-      <c r="F88">
-        <v>56.94</v>
-      </c>
-      <c r="G88">
-        <v>82.28</v>
-      </c>
-      <c r="H88">
-        <v>139.22</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89">
-        <v>1660</v>
-      </c>
-      <c r="B89">
-        <v>407</v>
-      </c>
-      <c r="C89">
-        <v>287</v>
-      </c>
-      <c r="D89">
-        <v>30.126927</v>
-      </c>
-      <c r="E89">
-        <v>74.161942</v>
-      </c>
-      <c r="F89">
-        <v>17.93</v>
-      </c>
-      <c r="G89">
-        <v>0</v>
-      </c>
-      <c r="H89">
-        <v>17.93</v>
+        <v>27.43</v>
       </c>
     </row>
   </sheetData>

--- a/pds_admin_Punjab_R/Backend/Backend/WB_Selected_Routes.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/WB_Selected_Routes.xlsx
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -426,36 +426,36 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>393</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>31.863261</v>
+        <v>31.781936</v>
       </c>
       <c r="E2">
-        <v>74.945286</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="F2">
-        <v>3.78</v>
+        <v>6.19</v>
       </c>
       <c r="G2">
-        <v>3.01</v>
+        <v>3.67</v>
       </c>
       <c r="H2">
-        <v>6.79</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -467,1240 +467,1240 @@
         <v>74.76758049999999</v>
       </c>
       <c r="F3">
-        <v>15.86</v>
+        <v>6.19</v>
       </c>
       <c r="G3">
-        <v>17.05</v>
+        <v>46.41</v>
       </c>
       <c r="H3">
-        <v>32.91</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="B4">
-        <v>396</v>
+        <v>23</v>
       </c>
       <c r="C4">
-        <v>280</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>30.154922</v>
+        <v>31.781936</v>
       </c>
       <c r="E4">
-        <v>74.193507</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="F4">
-        <v>0.28</v>
+        <v>6.19</v>
       </c>
       <c r="G4">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1.46</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
-        <v>501</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>398</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>286</v>
+        <v>393</v>
       </c>
       <c r="D5">
-        <v>30.15894356</v>
+        <v>31.863261</v>
       </c>
       <c r="E5">
-        <v>74.18094151</v>
+        <v>74.945286</v>
       </c>
       <c r="F5">
-        <v>1.44</v>
+        <v>3.78</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="H5">
-        <v>1.44</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>501</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>399</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>286</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>30.15894356</v>
+        <v>31.781936</v>
       </c>
       <c r="E6">
-        <v>74.18094151</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="F6">
-        <v>1.44</v>
+        <v>13.07</v>
       </c>
       <c r="G6">
-        <v>0.05</v>
+        <v>46.41</v>
       </c>
       <c r="H6">
-        <v>1.5</v>
+        <v>59.48</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7">
-        <v>501</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>400</v>
+        <v>23</v>
       </c>
       <c r="C7">
-        <v>286</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>30.15894356</v>
+        <v>31.781936</v>
       </c>
       <c r="E7">
-        <v>74.18094151</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="F7">
-        <v>1.44</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G7">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>3.07</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>501</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>405</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>280</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>30.154922</v>
+        <v>31.781936</v>
       </c>
       <c r="E8">
-        <v>74.193507</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="F8">
-        <v>0.28</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G8">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>1.36</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>501</v>
+        <v>1322</v>
       </c>
       <c r="B9">
-        <v>407</v>
+        <v>864</v>
       </c>
       <c r="C9">
-        <v>287</v>
+        <v>703</v>
       </c>
       <c r="D9">
-        <v>30.126927</v>
+        <v>30.618135</v>
       </c>
       <c r="E9">
-        <v>74.161942</v>
+        <v>75.435686</v>
       </c>
       <c r="F9">
-        <v>4.63</v>
+        <v>39.4</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>95.73</v>
       </c>
       <c r="H9">
-        <v>4.63</v>
+        <v>135.13</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>502</v>
+        <v>1322</v>
       </c>
       <c r="B10">
-        <v>394</v>
+        <v>865</v>
       </c>
       <c r="C10">
-        <v>281</v>
+        <v>703</v>
       </c>
       <c r="D10">
-        <v>30.090357</v>
+        <v>30.618135</v>
       </c>
       <c r="E10">
-        <v>74.20853700000001</v>
+        <v>75.435686</v>
       </c>
       <c r="F10">
-        <v>13.42</v>
+        <v>39.4</v>
       </c>
       <c r="G10">
-        <v>0.27</v>
+        <v>95.73</v>
       </c>
       <c r="H10">
-        <v>13.69</v>
+        <v>135.13</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>502</v>
+        <v>1322</v>
       </c>
       <c r="B11">
-        <v>397</v>
+        <v>866</v>
       </c>
       <c r="C11">
-        <v>282</v>
+        <v>703</v>
       </c>
       <c r="D11">
-        <v>30.100105</v>
+        <v>30.618135</v>
       </c>
       <c r="E11">
-        <v>74.20670699999999</v>
+        <v>75.435686</v>
       </c>
       <c r="F11">
-        <v>13.55</v>
+        <v>39.4</v>
       </c>
       <c r="G11">
-        <v>0.29</v>
+        <v>95.73</v>
       </c>
       <c r="H11">
-        <v>13.85</v>
+        <v>135.13</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>503</v>
+        <v>1322</v>
       </c>
       <c r="B12">
-        <v>404</v>
+        <v>868</v>
       </c>
       <c r="C12">
-        <v>283</v>
+        <v>703</v>
       </c>
       <c r="D12">
-        <v>30.105887</v>
+        <v>30.618135</v>
       </c>
       <c r="E12">
-        <v>74.18092900000001</v>
+        <v>75.435686</v>
       </c>
       <c r="F12">
-        <v>8.73</v>
+        <v>39.4</v>
       </c>
       <c r="G12">
-        <v>0.09</v>
+        <v>95.73</v>
       </c>
       <c r="H12">
-        <v>8.81</v>
+        <v>135.13</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>505</v>
+        <v>1322</v>
       </c>
       <c r="B13">
-        <v>407</v>
+        <v>869</v>
       </c>
       <c r="C13">
-        <v>287</v>
+        <v>703</v>
       </c>
       <c r="D13">
-        <v>30.126927</v>
+        <v>30.618135</v>
       </c>
       <c r="E13">
-        <v>74.161942</v>
+        <v>75.435686</v>
       </c>
       <c r="F13">
-        <v>16.9</v>
+        <v>39.4</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>95.73</v>
       </c>
       <c r="H13">
-        <v>16.9</v>
+        <v>135.13</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>506</v>
+        <v>1322</v>
       </c>
       <c r="B14">
-        <v>407</v>
+        <v>870</v>
       </c>
       <c r="C14">
-        <v>287</v>
+        <v>703</v>
       </c>
       <c r="D14">
-        <v>30.126927</v>
+        <v>30.618135</v>
       </c>
       <c r="E14">
-        <v>74.161942</v>
+        <v>75.435686</v>
       </c>
       <c r="F14">
-        <v>12.68</v>
+        <v>39.4</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>95.73</v>
       </c>
       <c r="H14">
-        <v>12.68</v>
+        <v>135.13</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>507</v>
+        <v>1322</v>
       </c>
       <c r="B15">
-        <v>394</v>
+        <v>871</v>
       </c>
       <c r="C15">
-        <v>281</v>
+        <v>703</v>
       </c>
       <c r="D15">
-        <v>30.090357</v>
+        <v>30.618135</v>
       </c>
       <c r="E15">
-        <v>74.20853700000001</v>
+        <v>75.435686</v>
       </c>
       <c r="F15">
-        <v>6.68</v>
+        <v>39.4</v>
       </c>
       <c r="G15">
-        <v>0.27</v>
+        <v>95.73</v>
       </c>
       <c r="H15">
-        <v>6.95</v>
+        <v>135.13</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>507</v>
+        <v>1322</v>
       </c>
       <c r="B16">
-        <v>395</v>
+        <v>872</v>
       </c>
       <c r="C16">
-        <v>281</v>
+        <v>703</v>
       </c>
       <c r="D16">
-        <v>30.090357</v>
+        <v>30.618135</v>
       </c>
       <c r="E16">
-        <v>74.20853700000001</v>
+        <v>75.435686</v>
       </c>
       <c r="F16">
-        <v>6.68</v>
+        <v>39.4</v>
       </c>
       <c r="G16">
-        <v>0.4</v>
+        <v>95.73</v>
       </c>
       <c r="H16">
-        <v>7.08</v>
+        <v>135.13</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>508</v>
+        <v>1322</v>
       </c>
       <c r="B17">
-        <v>403</v>
+        <v>873</v>
       </c>
       <c r="C17">
-        <v>284</v>
+        <v>703</v>
       </c>
       <c r="D17">
-        <v>30.163017</v>
+        <v>30.618135</v>
       </c>
       <c r="E17">
-        <v>74.186234</v>
+        <v>75.435686</v>
       </c>
       <c r="F17">
-        <v>13.62</v>
+        <v>39.4</v>
       </c>
       <c r="G17">
-        <v>0.72</v>
+        <v>95.73</v>
       </c>
       <c r="H17">
-        <v>14.33</v>
+        <v>135.13</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>508</v>
+        <v>1322</v>
       </c>
       <c r="B18">
-        <v>407</v>
+        <v>877</v>
       </c>
       <c r="C18">
-        <v>287</v>
+        <v>703</v>
       </c>
       <c r="D18">
-        <v>30.126927</v>
+        <v>30.618135</v>
       </c>
       <c r="E18">
-        <v>74.161942</v>
+        <v>75.435686</v>
       </c>
       <c r="F18">
-        <v>16.95</v>
+        <v>39.4</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>95.73</v>
       </c>
       <c r="H18">
-        <v>16.95</v>
+        <v>135.13</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>509</v>
+        <v>1323</v>
       </c>
       <c r="B19">
-        <v>400</v>
+        <v>867</v>
       </c>
       <c r="C19">
-        <v>285</v>
+        <v>999</v>
       </c>
       <c r="D19">
-        <v>30.180346</v>
+        <v>30.561546</v>
       </c>
       <c r="E19">
-        <v>74.17439299999999</v>
+        <v>75.352118</v>
       </c>
       <c r="F19">
-        <v>6.68</v>
+        <v>47.15</v>
       </c>
       <c r="G19">
-        <v>2.67</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H19">
-        <v>9.34</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>510</v>
+        <v>1323</v>
       </c>
       <c r="B20">
-        <v>407</v>
+        <v>875</v>
       </c>
       <c r="C20">
-        <v>287</v>
+        <v>999</v>
       </c>
       <c r="D20">
-        <v>30.126927</v>
+        <v>30.561546</v>
       </c>
       <c r="E20">
-        <v>74.161942</v>
+        <v>75.352118</v>
       </c>
       <c r="F20">
-        <v>16.65</v>
+        <v>47.15</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H20">
-        <v>16.65</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>511</v>
+        <v>1323</v>
       </c>
       <c r="B21">
-        <v>397</v>
+        <v>876</v>
       </c>
       <c r="C21">
-        <v>282</v>
+        <v>999</v>
       </c>
       <c r="D21">
-        <v>30.100105</v>
+        <v>30.561546</v>
       </c>
       <c r="E21">
-        <v>74.20670699999999</v>
+        <v>75.352118</v>
       </c>
       <c r="F21">
-        <v>12.02</v>
+        <v>47.15</v>
       </c>
       <c r="G21">
-        <v>0.29</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H21">
-        <v>12.31</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>512</v>
+        <v>1323</v>
       </c>
       <c r="B22">
-        <v>401</v>
+        <v>878</v>
       </c>
       <c r="C22">
-        <v>279</v>
+        <v>999</v>
       </c>
       <c r="D22">
-        <v>30.175344</v>
+        <v>30.561546</v>
       </c>
       <c r="E22">
-        <v>74.178363</v>
+        <v>75.352118</v>
       </c>
       <c r="F22">
-        <v>9.07</v>
+        <v>47.15</v>
       </c>
       <c r="G22">
-        <v>0.6</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H22">
-        <v>9.67</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>513</v>
+        <v>1323</v>
       </c>
       <c r="B23">
-        <v>407</v>
+        <v>879</v>
       </c>
       <c r="C23">
-        <v>287</v>
+        <v>999</v>
       </c>
       <c r="D23">
-        <v>30.126927</v>
+        <v>30.561546</v>
       </c>
       <c r="E23">
-        <v>74.161942</v>
+        <v>75.352118</v>
       </c>
       <c r="F23">
-        <v>16.24</v>
+        <v>47.15</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H23">
-        <v>16.24</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>514</v>
+        <v>1324</v>
       </c>
       <c r="B24">
-        <v>395</v>
+        <v>864</v>
       </c>
       <c r="C24">
-        <v>281</v>
+        <v>216</v>
       </c>
       <c r="D24">
-        <v>30.090357</v>
+        <v>30.5076194</v>
       </c>
       <c r="E24">
-        <v>74.20853700000001</v>
+        <v>74.958715</v>
       </c>
       <c r="F24">
-        <v>14.48</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="G24">
-        <v>0.4</v>
+        <v>48.72</v>
       </c>
       <c r="H24">
-        <v>14.88</v>
+        <v>128.79</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>515</v>
+        <v>1325</v>
       </c>
       <c r="B25">
-        <v>394</v>
+        <v>864</v>
       </c>
       <c r="C25">
-        <v>281</v>
+        <v>217</v>
       </c>
       <c r="D25">
-        <v>30.090357</v>
+        <v>30.51445</v>
       </c>
       <c r="E25">
-        <v>74.20853700000001</v>
+        <v>74.89836</v>
       </c>
       <c r="F25">
-        <v>7.77</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="G25">
-        <v>0.27</v>
+        <v>43.08</v>
       </c>
       <c r="H25">
-        <v>8.039999999999999</v>
+        <v>131.12</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>517</v>
+        <v>1326</v>
       </c>
       <c r="B26">
-        <v>400</v>
+        <v>866</v>
       </c>
       <c r="C26">
-        <v>285</v>
+        <v>57</v>
       </c>
       <c r="D26">
-        <v>30.180346</v>
+        <v>30.58822</v>
       </c>
       <c r="E26">
-        <v>74.17439299999999</v>
+        <v>75.6722</v>
       </c>
       <c r="F26">
-        <v>9.56</v>
+        <v>19.56</v>
       </c>
       <c r="G26">
-        <v>2.67</v>
+        <v>117.62</v>
       </c>
       <c r="H26">
-        <v>12.22</v>
+        <v>137.19</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>518</v>
+        <v>1326</v>
       </c>
       <c r="B27">
-        <v>403</v>
+        <v>874</v>
       </c>
       <c r="C27">
-        <v>284</v>
+        <v>57</v>
       </c>
       <c r="D27">
-        <v>30.163017</v>
+        <v>30.58822</v>
       </c>
       <c r="E27">
-        <v>74.186234</v>
+        <v>75.6722</v>
       </c>
       <c r="F27">
-        <v>6.29</v>
+        <v>19.56</v>
       </c>
       <c r="G27">
-        <v>0.72</v>
+        <v>117.62</v>
       </c>
       <c r="H27">
-        <v>7</v>
+        <v>137.19</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>520</v>
+        <v>1326</v>
       </c>
       <c r="B28">
-        <v>407</v>
+        <v>879</v>
       </c>
       <c r="C28">
-        <v>287</v>
+        <v>57</v>
       </c>
       <c r="D28">
-        <v>30.126927</v>
+        <v>30.58822</v>
       </c>
       <c r="E28">
-        <v>74.161942</v>
+        <v>75.6722</v>
       </c>
       <c r="F28">
-        <v>16.12</v>
+        <v>19.56</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>117.62</v>
       </c>
       <c r="H28">
-        <v>16.12</v>
+        <v>137.19</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>521</v>
+        <v>1327</v>
       </c>
       <c r="B29">
-        <v>402</v>
+        <v>866</v>
       </c>
       <c r="C29">
-        <v>285</v>
+        <v>217</v>
       </c>
       <c r="D29">
-        <v>30.180346</v>
+        <v>30.51445</v>
       </c>
       <c r="E29">
-        <v>74.17439299999999</v>
+        <v>74.89836</v>
       </c>
       <c r="F29">
-        <v>8.69</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="G29">
-        <v>0.4</v>
+        <v>43.08</v>
       </c>
       <c r="H29">
-        <v>9.09</v>
+        <v>125.59</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>522</v>
+        <v>1328</v>
       </c>
       <c r="B30">
-        <v>404</v>
+        <v>866</v>
       </c>
       <c r="C30">
-        <v>283</v>
+        <v>216</v>
       </c>
       <c r="D30">
-        <v>30.105887</v>
+        <v>30.5076194</v>
       </c>
       <c r="E30">
-        <v>74.18092900000001</v>
+        <v>74.958715</v>
       </c>
       <c r="F30">
-        <v>12.17</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G30">
-        <v>0.09</v>
+        <v>48.72</v>
       </c>
       <c r="H30">
-        <v>12.25</v>
+        <v>131.47</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>522</v>
+        <v>1328</v>
       </c>
       <c r="B31">
-        <v>407</v>
+        <v>880</v>
       </c>
       <c r="C31">
-        <v>287</v>
+        <v>216</v>
       </c>
       <c r="D31">
-        <v>30.126927</v>
+        <v>30.5076194</v>
       </c>
       <c r="E31">
-        <v>74.161942</v>
+        <v>74.958715</v>
       </c>
       <c r="F31">
-        <v>13.74</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>48.72</v>
       </c>
       <c r="H31">
-        <v>13.74</v>
+        <v>131.47</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>525</v>
+        <v>1329</v>
       </c>
       <c r="B32">
-        <v>407</v>
+        <v>877</v>
       </c>
       <c r="C32">
-        <v>287</v>
+        <v>678</v>
       </c>
       <c r="D32">
-        <v>30.126927</v>
+        <v>30.633572</v>
       </c>
       <c r="E32">
-        <v>74.161942</v>
+        <v>75.628421</v>
       </c>
       <c r="F32">
-        <v>9.449999999999999</v>
+        <v>24.17</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>114.19</v>
       </c>
       <c r="H32">
-        <v>9.449999999999999</v>
+        <v>138.36</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>526</v>
+        <v>1330</v>
       </c>
       <c r="B33">
-        <v>394</v>
+        <v>872</v>
       </c>
       <c r="C33">
-        <v>281</v>
+        <v>1225</v>
       </c>
       <c r="D33">
-        <v>30.090357</v>
+        <v>30.5792101</v>
       </c>
       <c r="E33">
-        <v>74.20853700000001</v>
+        <v>75.30097960000001</v>
       </c>
       <c r="F33">
-        <v>13.91</v>
+        <v>56.94</v>
       </c>
       <c r="G33">
-        <v>0.27</v>
+        <v>82.28</v>
       </c>
       <c r="H33">
-        <v>14.19</v>
+        <v>139.22</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>527</v>
+        <v>43</v>
       </c>
       <c r="B34">
-        <v>403</v>
+        <v>38</v>
       </c>
       <c r="C34">
-        <v>284</v>
+        <v>10</v>
       </c>
       <c r="D34">
-        <v>30.163017</v>
+        <v>31.571434</v>
       </c>
       <c r="E34">
-        <v>74.186234</v>
+        <v>75.048013</v>
       </c>
       <c r="F34">
-        <v>9.970000000000001</v>
+        <v>14.45</v>
       </c>
       <c r="G34">
-        <v>0.72</v>
+        <v>15.92</v>
       </c>
       <c r="H34">
-        <v>10.69</v>
+        <v>30.37</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>527</v>
+        <v>44</v>
       </c>
       <c r="B35">
-        <v>406</v>
+        <v>38</v>
       </c>
       <c r="C35">
-        <v>279</v>
+        <v>10</v>
       </c>
       <c r="D35">
-        <v>30.175344</v>
+        <v>31.571434</v>
       </c>
       <c r="E35">
-        <v>74.178363</v>
+        <v>75.048013</v>
       </c>
       <c r="F35">
-        <v>9.880000000000001</v>
+        <v>16.89</v>
       </c>
       <c r="G35">
-        <v>0.71</v>
+        <v>15.92</v>
       </c>
       <c r="H35">
-        <v>10.6</v>
+        <v>32.81</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>528</v>
+        <v>45</v>
       </c>
       <c r="B36">
-        <v>397</v>
+        <v>15</v>
       </c>
       <c r="C36">
-        <v>282</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>30.100105</v>
+        <v>31.67995</v>
       </c>
       <c r="E36">
-        <v>74.20670699999999</v>
+        <v>74.84148999999999</v>
       </c>
       <c r="F36">
-        <v>13.64</v>
+        <v>13.14</v>
       </c>
       <c r="G36">
-        <v>0.29</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H36">
-        <v>13.94</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>528</v>
+        <v>45</v>
       </c>
       <c r="B37">
-        <v>407</v>
+        <v>16</v>
       </c>
       <c r="C37">
-        <v>287</v>
+        <v>2</v>
       </c>
       <c r="D37">
-        <v>30.126927</v>
+        <v>31.67995</v>
       </c>
       <c r="E37">
-        <v>74.161942</v>
+        <v>74.84148999999999</v>
       </c>
       <c r="F37">
-        <v>17.47</v>
+        <v>13.14</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H37">
-        <v>17.47</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>529</v>
+        <v>45</v>
       </c>
       <c r="B38">
-        <v>407</v>
+        <v>38</v>
       </c>
       <c r="C38">
-        <v>287</v>
+        <v>1933</v>
       </c>
       <c r="D38">
-        <v>30.126927</v>
+        <v>31.486005</v>
       </c>
       <c r="E38">
-        <v>74.161942</v>
+        <v>74.955196</v>
       </c>
       <c r="F38">
-        <v>18.37</v>
+        <v>29.59</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>7.51</v>
       </c>
       <c r="H38">
-        <v>18.37</v>
+        <v>37.11</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>531</v>
+        <v>45</v>
       </c>
       <c r="B39">
-        <v>400</v>
+        <v>39</v>
       </c>
       <c r="C39">
-        <v>285</v>
+        <v>1933</v>
       </c>
       <c r="D39">
-        <v>30.180346</v>
+        <v>31.486005</v>
       </c>
       <c r="E39">
-        <v>74.17439299999999</v>
+        <v>74.955196</v>
       </c>
       <c r="F39">
-        <v>6.95</v>
+        <v>29.59</v>
       </c>
       <c r="G39">
-        <v>2.67</v>
+        <v>7.51</v>
       </c>
       <c r="H39">
-        <v>9.619999999999999</v>
+        <v>37.11</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>532</v>
+        <v>46</v>
       </c>
       <c r="B40">
-        <v>407</v>
+        <v>15</v>
       </c>
       <c r="C40">
-        <v>287</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>30.126927</v>
+        <v>31.67995</v>
       </c>
       <c r="E40">
-        <v>74.161942</v>
+        <v>74.84148999999999</v>
       </c>
       <c r="F40">
-        <v>10.93</v>
+        <v>9.75</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H40">
-        <v>10.93</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>533</v>
+        <v>46</v>
       </c>
       <c r="B41">
-        <v>407</v>
+        <v>45</v>
       </c>
       <c r="C41">
-        <v>287</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>30.126927</v>
+        <v>31.67995</v>
       </c>
       <c r="E41">
-        <v>74.161942</v>
+        <v>74.84148999999999</v>
       </c>
       <c r="F41">
-        <v>13.39</v>
+        <v>9.75</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>35.06</v>
       </c>
       <c r="H41">
-        <v>13.39</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>534</v>
+        <v>46</v>
       </c>
       <c r="B42">
-        <v>407</v>
+        <v>46</v>
       </c>
       <c r="C42">
-        <v>287</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>30.126927</v>
+        <v>31.67995</v>
       </c>
       <c r="E42">
-        <v>74.161942</v>
+        <v>74.84148999999999</v>
       </c>
       <c r="F42">
-        <v>11.24</v>
+        <v>9.75</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>35.06</v>
       </c>
       <c r="H42">
-        <v>11.24</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>535</v>
+        <v>501</v>
       </c>
       <c r="B43">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C43">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D43">
-        <v>30.126927</v>
+        <v>30.154922</v>
       </c>
       <c r="E43">
-        <v>74.161942</v>
+        <v>74.193507</v>
       </c>
       <c r="F43">
-        <v>5.65</v>
+        <v>0.28</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="H43">
-        <v>5.65</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="B44">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C44">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D44">
-        <v>30.126927</v>
+        <v>30.15894356</v>
       </c>
       <c r="E44">
-        <v>74.161942</v>
+        <v>74.18094151</v>
       </c>
       <c r="F44">
-        <v>13.52</v>
+        <v>1.44</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>13.52</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>540</v>
+        <v>501</v>
       </c>
       <c r="B45">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C45">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D45">
-        <v>30.105887</v>
+        <v>30.15894356</v>
       </c>
       <c r="E45">
-        <v>74.18092900000001</v>
+        <v>74.18094151</v>
       </c>
       <c r="F45">
-        <v>13.62</v>
+        <v>1.44</v>
       </c>
       <c r="G45">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H45">
-        <v>13.71</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>541</v>
+        <v>501</v>
       </c>
       <c r="B46">
         <v>400</v>
       </c>
       <c r="C46">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D46">
-        <v>30.180346</v>
+        <v>30.15894356</v>
       </c>
       <c r="E46">
-        <v>74.17439299999999</v>
+        <v>74.18094151</v>
       </c>
       <c r="F46">
-        <v>9.44</v>
+        <v>1.44</v>
       </c>
       <c r="G46">
-        <v>2.67</v>
+        <v>1.63</v>
       </c>
       <c r="H46">
-        <v>12.11</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>542</v>
+        <v>501</v>
       </c>
       <c r="B47">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C47">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D47">
-        <v>30.180346</v>
+        <v>30.163017</v>
       </c>
       <c r="E47">
-        <v>74.17439299999999</v>
+        <v>74.186234</v>
       </c>
       <c r="F47">
-        <v>8.66</v>
+        <v>1.16</v>
       </c>
       <c r="G47">
-        <v>2.67</v>
+        <v>0.72</v>
       </c>
       <c r="H47">
-        <v>11.33</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>543</v>
+        <v>501</v>
       </c>
       <c r="B48">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C48">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D48">
-        <v>30.180346</v>
+        <v>30.154922</v>
       </c>
       <c r="E48">
-        <v>74.17439299999999</v>
+        <v>74.193507</v>
       </c>
       <c r="F48">
-        <v>9.58</v>
+        <v>0.28</v>
       </c>
       <c r="G48">
-        <v>2.67</v>
+        <v>1.07</v>
       </c>
       <c r="H48">
-        <v>12.25</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>545</v>
+        <v>502</v>
       </c>
       <c r="B49">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C49">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D49">
-        <v>30.105887</v>
+        <v>30.126927</v>
       </c>
       <c r="E49">
-        <v>74.18092900000001</v>
+        <v>74.161942</v>
       </c>
       <c r="F49">
-        <v>14.61</v>
+        <v>18.11</v>
       </c>
       <c r="G49">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>14.7</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>546</v>
+        <v>503</v>
       </c>
       <c r="B50">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C50">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D50">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="E50">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="F50">
-        <v>4.23</v>
+        <v>8.73</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="H50">
-        <v>4.23</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>547</v>
+        <v>503</v>
       </c>
       <c r="B51">
         <v>407</v>
@@ -1715,18 +1715,18 @@
         <v>74.161942</v>
       </c>
       <c r="F51">
-        <v>17.22</v>
+        <v>11.44</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>17.22</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>548</v>
+        <v>505</v>
       </c>
       <c r="B52">
         <v>407</v>
@@ -1741,200 +1741,200 @@
         <v>74.161942</v>
       </c>
       <c r="F52">
-        <v>16.25</v>
+        <v>16.9</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>16.25</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>549</v>
+        <v>506</v>
       </c>
       <c r="B53">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C53">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D53">
-        <v>30.175344</v>
+        <v>30.163017</v>
       </c>
       <c r="E53">
-        <v>74.178363</v>
+        <v>74.186234</v>
       </c>
       <c r="F53">
-        <v>15.77</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G53">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="H53">
-        <v>16.37</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>550</v>
+        <v>506</v>
       </c>
       <c r="B54">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C54">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D54">
-        <v>30.180346</v>
+        <v>30.163017</v>
       </c>
       <c r="E54">
-        <v>74.17439299999999</v>
+        <v>74.186234</v>
       </c>
       <c r="F54">
-        <v>11.65</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G54">
-        <v>2.67</v>
+        <v>0.85</v>
       </c>
       <c r="H54">
-        <v>14.32</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>550</v>
+        <v>507</v>
       </c>
       <c r="B55">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C55">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D55">
-        <v>30.180346</v>
+        <v>30.090357</v>
       </c>
       <c r="E55">
-        <v>74.17439299999999</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="F55">
-        <v>11.65</v>
+        <v>6.68</v>
       </c>
       <c r="G55">
         <v>0.4</v>
       </c>
       <c r="H55">
-        <v>12.06</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>551</v>
+        <v>508</v>
       </c>
       <c r="B56">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C56">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D56">
-        <v>30.175344</v>
+        <v>30.163017</v>
       </c>
       <c r="E56">
-        <v>74.178363</v>
+        <v>74.186234</v>
       </c>
       <c r="F56">
-        <v>12.91</v>
+        <v>13.62</v>
       </c>
       <c r="G56">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="H56">
-        <v>13.51</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>552</v>
+        <v>509</v>
       </c>
       <c r="B57">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C57">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D57">
-        <v>30.175344</v>
+        <v>30.180346</v>
       </c>
       <c r="E57">
-        <v>74.178363</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F57">
-        <v>13.44</v>
+        <v>6.68</v>
       </c>
       <c r="G57">
-        <v>0.6</v>
+        <v>2.67</v>
       </c>
       <c r="H57">
-        <v>14.04</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="B58">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C58">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D58">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="E58">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="F58">
-        <v>17.49</v>
+        <v>16.65</v>
       </c>
       <c r="G58">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>20.16</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>565</v>
+        <v>511</v>
       </c>
       <c r="B59">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C59">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D59">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="E59">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="F59">
-        <v>15.83</v>
+        <v>16.06</v>
       </c>
       <c r="G59">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>18.5</v>
+        <v>16.06</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>612</v>
+        <v>512</v>
       </c>
       <c r="B60">
         <v>401</v>
@@ -1949,637 +1949,2431 @@
         <v>74.178363</v>
       </c>
       <c r="F60">
-        <v>15.13</v>
+        <v>9.07</v>
       </c>
       <c r="G60">
         <v>0.6</v>
       </c>
       <c r="H60">
-        <v>15.73</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>1046</v>
+        <v>513</v>
       </c>
       <c r="B61">
-        <v>625</v>
+        <v>407</v>
       </c>
       <c r="C61">
-        <v>522</v>
+        <v>287</v>
       </c>
       <c r="D61">
-        <v>31.4204409</v>
+        <v>30.126927</v>
       </c>
       <c r="E61">
-        <v>75.69994199999999</v>
+        <v>74.161942</v>
       </c>
       <c r="F61">
-        <v>1.94</v>
+        <v>16.24</v>
       </c>
       <c r="G61">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>3.8</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>1577</v>
+        <v>514</v>
       </c>
       <c r="B62">
-        <v>866</v>
+        <v>404</v>
       </c>
       <c r="C62">
-        <v>1455</v>
+        <v>283</v>
       </c>
       <c r="D62">
-        <v>30.450458</v>
+        <v>30.105887</v>
       </c>
       <c r="E62">
-        <v>74.489422</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="F62">
-        <v>7.65</v>
+        <v>16.59</v>
       </c>
       <c r="G62">
-        <v>3.55</v>
+        <v>0.09</v>
       </c>
       <c r="H62">
-        <v>11.2</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>1577</v>
+        <v>515</v>
       </c>
       <c r="B63">
-        <v>870</v>
+        <v>397</v>
       </c>
       <c r="C63">
-        <v>1455</v>
+        <v>282</v>
       </c>
       <c r="D63">
-        <v>30.450458</v>
+        <v>30.100105</v>
       </c>
       <c r="E63">
-        <v>74.489422</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="F63">
-        <v>7.65</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G63">
-        <v>3.55</v>
+        <v>0.29</v>
       </c>
       <c r="H63">
-        <v>11.2</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>1577</v>
+        <v>515</v>
       </c>
       <c r="B64">
-        <v>875</v>
+        <v>407</v>
       </c>
       <c r="C64">
-        <v>1455</v>
+        <v>287</v>
       </c>
       <c r="D64">
-        <v>30.450458</v>
+        <v>30.126927</v>
       </c>
       <c r="E64">
-        <v>74.489422</v>
+        <v>74.161942</v>
       </c>
       <c r="F64">
-        <v>7.65</v>
+        <v>13.16</v>
       </c>
       <c r="G64">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>11.2</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>1577</v>
+        <v>516</v>
       </c>
       <c r="B65">
-        <v>876</v>
+        <v>401</v>
       </c>
       <c r="C65">
-        <v>1455</v>
+        <v>279</v>
       </c>
       <c r="D65">
-        <v>30.450458</v>
+        <v>30.175344</v>
       </c>
       <c r="E65">
-        <v>74.489422</v>
+        <v>74.178363</v>
       </c>
       <c r="F65">
-        <v>7.65</v>
+        <v>17.41</v>
       </c>
       <c r="G65">
-        <v>3.55</v>
+        <v>0.6</v>
       </c>
       <c r="H65">
-        <v>11.2</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>1597</v>
+        <v>516</v>
       </c>
       <c r="B66">
-        <v>866</v>
+        <v>406</v>
       </c>
       <c r="C66">
-        <v>1455</v>
+        <v>284</v>
       </c>
       <c r="D66">
-        <v>30.450458</v>
+        <v>30.163017</v>
       </c>
       <c r="E66">
-        <v>74.489422</v>
+        <v>74.186234</v>
       </c>
       <c r="F66">
-        <v>5.62</v>
+        <v>17.16</v>
       </c>
       <c r="G66">
-        <v>3.55</v>
+        <v>0.85</v>
       </c>
       <c r="H66">
-        <v>9.17</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>1597</v>
+        <v>517</v>
       </c>
       <c r="B67">
-        <v>872</v>
+        <v>400</v>
       </c>
       <c r="C67">
-        <v>1455</v>
+        <v>285</v>
       </c>
       <c r="D67">
-        <v>30.450458</v>
+        <v>30.180346</v>
       </c>
       <c r="E67">
-        <v>74.489422</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F67">
-        <v>5.62</v>
+        <v>9.56</v>
       </c>
       <c r="G67">
-        <v>3.55</v>
+        <v>2.67</v>
       </c>
       <c r="H67">
-        <v>9.17</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>1597</v>
+        <v>518</v>
       </c>
       <c r="B68">
-        <v>877</v>
+        <v>406</v>
       </c>
       <c r="C68">
-        <v>1455</v>
+        <v>284</v>
       </c>
       <c r="D68">
-        <v>30.450458</v>
+        <v>30.163017</v>
       </c>
       <c r="E68">
-        <v>74.489422</v>
+        <v>74.186234</v>
       </c>
       <c r="F68">
-        <v>5.62</v>
+        <v>6.29</v>
       </c>
       <c r="G68">
-        <v>3.55</v>
+        <v>0.85</v>
       </c>
       <c r="H68">
-        <v>9.17</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>1607</v>
+        <v>520</v>
       </c>
       <c r="B69">
-        <v>864</v>
+        <v>400</v>
       </c>
       <c r="C69">
-        <v>1512</v>
+        <v>285</v>
       </c>
       <c r="D69">
-        <v>30.4713293</v>
+        <v>30.180346</v>
       </c>
       <c r="E69">
-        <v>74.5033904</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F69">
-        <v>0.21</v>
+        <v>14.76</v>
       </c>
       <c r="G69">
-        <v>4.99</v>
+        <v>2.67</v>
       </c>
       <c r="H69">
-        <v>5.2</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>1607</v>
+        <v>520</v>
       </c>
       <c r="B70">
-        <v>865</v>
+        <v>407</v>
       </c>
       <c r="C70">
-        <v>1512</v>
+        <v>287</v>
       </c>
       <c r="D70">
-        <v>30.4713293</v>
+        <v>30.126927</v>
       </c>
       <c r="E70">
-        <v>74.5033904</v>
+        <v>74.161942</v>
       </c>
       <c r="F70">
-        <v>0.21</v>
+        <v>16.12</v>
       </c>
       <c r="G70">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>5.2</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>1607</v>
+        <v>521</v>
       </c>
       <c r="B71">
-        <v>867</v>
+        <v>401</v>
       </c>
       <c r="C71">
-        <v>1512</v>
+        <v>279</v>
       </c>
       <c r="D71">
-        <v>30.4713293</v>
+        <v>30.175344</v>
       </c>
       <c r="E71">
-        <v>74.5033904</v>
+        <v>74.178363</v>
       </c>
       <c r="F71">
-        <v>0.21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G71">
-        <v>4.99</v>
+        <v>0.6</v>
       </c>
       <c r="H71">
-        <v>5.2</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>1607</v>
+        <v>521</v>
       </c>
       <c r="B72">
-        <v>868</v>
+        <v>402</v>
       </c>
       <c r="C72">
-        <v>1512</v>
+        <v>285</v>
       </c>
       <c r="D72">
-        <v>30.4713293</v>
+        <v>30.180346</v>
       </c>
       <c r="E72">
-        <v>74.5033904</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F72">
-        <v>0.21</v>
+        <v>8.69</v>
       </c>
       <c r="G72">
-        <v>4.99</v>
+        <v>0.4</v>
       </c>
       <c r="H72">
-        <v>5.2</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>1607</v>
+        <v>522</v>
       </c>
       <c r="B73">
-        <v>869</v>
+        <v>407</v>
       </c>
       <c r="C73">
-        <v>1512</v>
+        <v>287</v>
       </c>
       <c r="D73">
-        <v>30.4713293</v>
+        <v>30.126927</v>
       </c>
       <c r="E73">
-        <v>74.5033904</v>
+        <v>74.161942</v>
       </c>
       <c r="F73">
-        <v>0.21</v>
+        <v>13.74</v>
       </c>
       <c r="G73">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>5.2</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>1607</v>
+        <v>523</v>
       </c>
       <c r="B74">
-        <v>871</v>
+        <v>407</v>
       </c>
       <c r="C74">
-        <v>1512</v>
+        <v>287</v>
       </c>
       <c r="D74">
-        <v>30.4713293</v>
+        <v>30.126927</v>
       </c>
       <c r="E74">
-        <v>74.5033904</v>
+        <v>74.161942</v>
       </c>
       <c r="F74">
-        <v>0.21</v>
+        <v>22.2</v>
       </c>
       <c r="G74">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>5.2</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>1607</v>
+        <v>524</v>
       </c>
       <c r="B75">
-        <v>873</v>
+        <v>397</v>
       </c>
       <c r="C75">
-        <v>1512</v>
+        <v>281</v>
       </c>
       <c r="D75">
-        <v>30.4713293</v>
+        <v>30.090357</v>
       </c>
       <c r="E75">
-        <v>74.5033904</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="F75">
-        <v>0.21</v>
+        <v>23.25</v>
       </c>
       <c r="G75">
-        <v>4.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H75">
-        <v>5.2</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>1607</v>
+        <v>525</v>
       </c>
       <c r="B76">
-        <v>874</v>
+        <v>407</v>
       </c>
       <c r="C76">
-        <v>1512</v>
+        <v>287</v>
       </c>
       <c r="D76">
-        <v>30.4713293</v>
+        <v>30.126927</v>
       </c>
       <c r="E76">
-        <v>74.5033904</v>
+        <v>74.161942</v>
       </c>
       <c r="F76">
-        <v>0.21</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G76">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="H76">
-        <v>5.2</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>1607</v>
+        <v>526</v>
       </c>
       <c r="B77">
-        <v>877</v>
+        <v>394</v>
       </c>
       <c r="C77">
-        <v>1512</v>
+        <v>281</v>
       </c>
       <c r="D77">
-        <v>30.4713293</v>
+        <v>30.090357</v>
       </c>
       <c r="E77">
-        <v>74.5033904</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="F77">
-        <v>0.21</v>
+        <v>13.91</v>
       </c>
       <c r="G77">
-        <v>4.99</v>
+        <v>0.27</v>
       </c>
       <c r="H77">
-        <v>5.2</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>1607</v>
+        <v>526</v>
       </c>
       <c r="B78">
-        <v>878</v>
+        <v>395</v>
       </c>
       <c r="C78">
-        <v>1512</v>
+        <v>281</v>
       </c>
       <c r="D78">
-        <v>30.4713293</v>
+        <v>30.090357</v>
       </c>
       <c r="E78">
-        <v>74.5033904</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="F78">
-        <v>0.21</v>
+        <v>13.91</v>
       </c>
       <c r="G78">
-        <v>4.99</v>
+        <v>0.4</v>
       </c>
       <c r="H78">
-        <v>5.2</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>1607</v>
+        <v>527</v>
       </c>
       <c r="B79">
-        <v>879</v>
+        <v>401</v>
       </c>
       <c r="C79">
-        <v>1512</v>
+        <v>279</v>
       </c>
       <c r="D79">
-        <v>30.4713293</v>
+        <v>30.175344</v>
       </c>
       <c r="E79">
-        <v>74.5033904</v>
+        <v>74.178363</v>
       </c>
       <c r="F79">
-        <v>0.21</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G79">
-        <v>4.99</v>
+        <v>0.6</v>
       </c>
       <c r="H79">
-        <v>5.2</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>1607</v>
+        <v>528</v>
       </c>
       <c r="B80">
-        <v>880</v>
+        <v>407</v>
       </c>
       <c r="C80">
-        <v>1512</v>
+        <v>287</v>
       </c>
       <c r="D80">
-        <v>30.4713293</v>
+        <v>30.126927</v>
       </c>
       <c r="E80">
-        <v>74.5033904</v>
+        <v>74.161942</v>
       </c>
       <c r="F80">
-        <v>0.21</v>
+        <v>17.47</v>
       </c>
       <c r="G80">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="H80">
-        <v>5.2</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>1660</v>
+        <v>529</v>
       </c>
       <c r="B81">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C81">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D81">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="E81">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="F81">
-        <v>13.33</v>
+        <v>18.37</v>
       </c>
       <c r="G81">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>13.93</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>1660</v>
+        <v>530</v>
       </c>
       <c r="B82">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C82">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D82">
-        <v>30.175344</v>
+        <v>30.090357</v>
       </c>
       <c r="E82">
-        <v>74.178363</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="F82">
-        <v>13.33</v>
+        <v>19.1</v>
       </c>
       <c r="G82">
-        <v>0.71</v>
+        <v>0.27</v>
       </c>
       <c r="H82">
-        <v>14.04</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>2153</v>
+        <v>531</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="C83">
-        <v>1948</v>
+        <v>285</v>
       </c>
       <c r="D83">
-        <v>31.361236</v>
+        <v>30.180346</v>
       </c>
       <c r="E83">
-        <v>74.66727400000001</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="F83">
-        <v>5.71</v>
+        <v>6.95</v>
       </c>
       <c r="G83">
-        <v>21.72</v>
+        <v>2.67</v>
       </c>
       <c r="H83">
-        <v>27.43</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
+        <v>532</v>
+      </c>
+      <c r="B84">
+        <v>407</v>
+      </c>
+      <c r="C84">
+        <v>287</v>
+      </c>
+      <c r="D84">
+        <v>30.126927</v>
+      </c>
+      <c r="E84">
+        <v>74.161942</v>
+      </c>
+      <c r="F84">
+        <v>10.93</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>10.93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85">
+        <v>533</v>
+      </c>
+      <c r="B85">
+        <v>407</v>
+      </c>
+      <c r="C85">
+        <v>287</v>
+      </c>
+      <c r="D85">
+        <v>30.126927</v>
+      </c>
+      <c r="E85">
+        <v>74.161942</v>
+      </c>
+      <c r="F85">
+        <v>13.39</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>13.39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86">
+        <v>534</v>
+      </c>
+      <c r="B86">
+        <v>407</v>
+      </c>
+      <c r="C86">
+        <v>287</v>
+      </c>
+      <c r="D86">
+        <v>30.126927</v>
+      </c>
+      <c r="E86">
+        <v>74.161942</v>
+      </c>
+      <c r="F86">
+        <v>11.24</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>11.24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87">
+        <v>535</v>
+      </c>
+      <c r="B87">
+        <v>407</v>
+      </c>
+      <c r="C87">
+        <v>287</v>
+      </c>
+      <c r="D87">
+        <v>30.126927</v>
+      </c>
+      <c r="E87">
+        <v>74.161942</v>
+      </c>
+      <c r="F87">
+        <v>5.65</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88">
+        <v>536</v>
+      </c>
+      <c r="B88">
+        <v>394</v>
+      </c>
+      <c r="C88">
+        <v>281</v>
+      </c>
+      <c r="D88">
+        <v>30.090357</v>
+      </c>
+      <c r="E88">
+        <v>74.20853700000001</v>
+      </c>
+      <c r="F88">
+        <v>16.79</v>
+      </c>
+      <c r="G88">
+        <v>0.27</v>
+      </c>
+      <c r="H88">
+        <v>17.06</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89">
+        <v>536</v>
+      </c>
+      <c r="B89">
+        <v>397</v>
+      </c>
+      <c r="C89">
+        <v>281</v>
+      </c>
+      <c r="D89">
+        <v>30.090357</v>
+      </c>
+      <c r="E89">
+        <v>74.20853700000001</v>
+      </c>
+      <c r="F89">
+        <v>16.79</v>
+      </c>
+      <c r="G89">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H89">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90">
+        <v>537</v>
+      </c>
+      <c r="B90">
+        <v>394</v>
+      </c>
+      <c r="C90">
+        <v>281</v>
+      </c>
+      <c r="D90">
+        <v>30.090357</v>
+      </c>
+      <c r="E90">
+        <v>74.20853700000001</v>
+      </c>
+      <c r="F90">
+        <v>22.65</v>
+      </c>
+      <c r="G90">
+        <v>0.27</v>
+      </c>
+      <c r="H90">
+        <v>22.93</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91">
+        <v>538</v>
+      </c>
+      <c r="B91">
+        <v>407</v>
+      </c>
+      <c r="C91">
+        <v>287</v>
+      </c>
+      <c r="D91">
+        <v>30.126927</v>
+      </c>
+      <c r="E91">
+        <v>74.161942</v>
+      </c>
+      <c r="F91">
+        <v>13.52</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>13.52</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92">
+        <v>540</v>
+      </c>
+      <c r="B92">
+        <v>407</v>
+      </c>
+      <c r="C92">
+        <v>287</v>
+      </c>
+      <c r="D92">
+        <v>30.126927</v>
+      </c>
+      <c r="E92">
+        <v>74.161942</v>
+      </c>
+      <c r="F92">
+        <v>15.98</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>15.98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93">
+        <v>541</v>
+      </c>
+      <c r="B93">
+        <v>400</v>
+      </c>
+      <c r="C93">
+        <v>285</v>
+      </c>
+      <c r="D93">
+        <v>30.180346</v>
+      </c>
+      <c r="E93">
+        <v>74.17439299999999</v>
+      </c>
+      <c r="F93">
+        <v>9.44</v>
+      </c>
+      <c r="G93">
+        <v>2.67</v>
+      </c>
+      <c r="H93">
+        <v>12.11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94">
+        <v>542</v>
+      </c>
+      <c r="B94">
+        <v>400</v>
+      </c>
+      <c r="C94">
+        <v>285</v>
+      </c>
+      <c r="D94">
+        <v>30.180346</v>
+      </c>
+      <c r="E94">
+        <v>74.17439299999999</v>
+      </c>
+      <c r="F94">
+        <v>8.66</v>
+      </c>
+      <c r="G94">
+        <v>2.67</v>
+      </c>
+      <c r="H94">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95">
+        <v>543</v>
+      </c>
+      <c r="B95">
+        <v>400</v>
+      </c>
+      <c r="C95">
+        <v>285</v>
+      </c>
+      <c r="D95">
+        <v>30.180346</v>
+      </c>
+      <c r="E95">
+        <v>74.17439299999999</v>
+      </c>
+      <c r="F95">
+        <v>9.58</v>
+      </c>
+      <c r="G95">
+        <v>2.67</v>
+      </c>
+      <c r="H95">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96">
+        <v>545</v>
+      </c>
+      <c r="B96">
+        <v>407</v>
+      </c>
+      <c r="C96">
+        <v>287</v>
+      </c>
+      <c r="D96">
+        <v>30.126927</v>
+      </c>
+      <c r="E96">
+        <v>74.161942</v>
+      </c>
+      <c r="F96">
+        <v>16.86</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>16.86</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97">
+        <v>546</v>
+      </c>
+      <c r="B97">
+        <v>407</v>
+      </c>
+      <c r="C97">
+        <v>287</v>
+      </c>
+      <c r="D97">
+        <v>30.126927</v>
+      </c>
+      <c r="E97">
+        <v>74.161942</v>
+      </c>
+      <c r="F97">
+        <v>4.23</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98">
+        <v>547</v>
+      </c>
+      <c r="B98">
+        <v>407</v>
+      </c>
+      <c r="C98">
+        <v>287</v>
+      </c>
+      <c r="D98">
+        <v>30.126927</v>
+      </c>
+      <c r="E98">
+        <v>74.161942</v>
+      </c>
+      <c r="F98">
+        <v>17.22</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99">
+        <v>548</v>
+      </c>
+      <c r="B99">
+        <v>400</v>
+      </c>
+      <c r="C99">
+        <v>285</v>
+      </c>
+      <c r="D99">
+        <v>30.180346</v>
+      </c>
+      <c r="E99">
+        <v>74.17439299999999</v>
+      </c>
+      <c r="F99">
+        <v>14.86</v>
+      </c>
+      <c r="G99">
+        <v>2.67</v>
+      </c>
+      <c r="H99">
+        <v>17.53</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100">
+        <v>549</v>
+      </c>
+      <c r="B100">
+        <v>401</v>
+      </c>
+      <c r="C100">
+        <v>279</v>
+      </c>
+      <c r="D100">
+        <v>30.175344</v>
+      </c>
+      <c r="E100">
+        <v>74.178363</v>
+      </c>
+      <c r="F100">
+        <v>15.77</v>
+      </c>
+      <c r="G100">
+        <v>0.6</v>
+      </c>
+      <c r="H100">
+        <v>16.37</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101">
+        <v>550</v>
+      </c>
+      <c r="B101">
+        <v>402</v>
+      </c>
+      <c r="C101">
+        <v>285</v>
+      </c>
+      <c r="D101">
+        <v>30.180346</v>
+      </c>
+      <c r="E101">
+        <v>74.17439299999999</v>
+      </c>
+      <c r="F101">
+        <v>11.65</v>
+      </c>
+      <c r="G101">
+        <v>0.4</v>
+      </c>
+      <c r="H101">
+        <v>12.06</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102">
+        <v>551</v>
+      </c>
+      <c r="B102">
+        <v>401</v>
+      </c>
+      <c r="C102">
+        <v>279</v>
+      </c>
+      <c r="D102">
+        <v>30.175344</v>
+      </c>
+      <c r="E102">
+        <v>74.178363</v>
+      </c>
+      <c r="F102">
+        <v>12.91</v>
+      </c>
+      <c r="G102">
+        <v>0.6</v>
+      </c>
+      <c r="H102">
+        <v>13.51</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103">
+        <v>552</v>
+      </c>
+      <c r="B103">
+        <v>401</v>
+      </c>
+      <c r="C103">
+        <v>279</v>
+      </c>
+      <c r="D103">
+        <v>30.175344</v>
+      </c>
+      <c r="E103">
+        <v>74.178363</v>
+      </c>
+      <c r="F103">
+        <v>13.44</v>
+      </c>
+      <c r="G103">
+        <v>0.6</v>
+      </c>
+      <c r="H103">
+        <v>14.04</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104">
+        <v>1046</v>
+      </c>
+      <c r="B104">
+        <v>625</v>
+      </c>
+      <c r="C104">
+        <v>522</v>
+      </c>
+      <c r="D104">
+        <v>31.4204409</v>
+      </c>
+      <c r="E104">
+        <v>75.69994199999999</v>
+      </c>
+      <c r="F104">
+        <v>1.94</v>
+      </c>
+      <c r="G104">
+        <v>1.86</v>
+      </c>
+      <c r="H104">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105">
+        <v>54</v>
+      </c>
+      <c r="B105">
+        <v>21</v>
+      </c>
+      <c r="C105">
+        <v>392</v>
+      </c>
+      <c r="D105">
+        <v>31.72093</v>
+      </c>
+      <c r="E105">
+        <v>75.30386</v>
+      </c>
+      <c r="F105">
+        <v>12.09</v>
+      </c>
+      <c r="G105">
+        <v>9.07</v>
+      </c>
+      <c r="H105">
+        <v>21.16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106">
+        <v>54</v>
+      </c>
+      <c r="B106">
+        <v>29</v>
+      </c>
+      <c r="C106">
+        <v>8</v>
+      </c>
+      <c r="D106">
+        <v>31.554916</v>
+      </c>
+      <c r="E106">
+        <v>75.184044</v>
+      </c>
+      <c r="F106">
+        <v>15.04</v>
+      </c>
+      <c r="G106">
+        <v>4.24</v>
+      </c>
+      <c r="H106">
+        <v>19.27</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107">
+        <v>54</v>
+      </c>
+      <c r="B107">
+        <v>37</v>
+      </c>
+      <c r="C107">
+        <v>8</v>
+      </c>
+      <c r="D107">
+        <v>31.554916</v>
+      </c>
+      <c r="E107">
+        <v>75.184044</v>
+      </c>
+      <c r="F107">
+        <v>15.04</v>
+      </c>
+      <c r="G107">
+        <v>0.03</v>
+      </c>
+      <c r="H107">
+        <v>15.07</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108">
+        <v>54</v>
+      </c>
+      <c r="B108">
+        <v>44</v>
+      </c>
+      <c r="C108">
+        <v>7</v>
+      </c>
+      <c r="D108">
+        <v>31.539066</v>
+      </c>
+      <c r="E108">
+        <v>75.244698</v>
+      </c>
+      <c r="F108">
+        <v>11.4</v>
+      </c>
+      <c r="G108">
+        <v>4.92</v>
+      </c>
+      <c r="H108">
+        <v>16.31</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109">
+        <v>55</v>
+      </c>
+      <c r="B109">
+        <v>29</v>
+      </c>
+      <c r="C109">
+        <v>8</v>
+      </c>
+      <c r="D109">
+        <v>31.554916</v>
+      </c>
+      <c r="E109">
+        <v>75.184044</v>
+      </c>
+      <c r="F109">
+        <v>5.14</v>
+      </c>
+      <c r="G109">
+        <v>4.24</v>
+      </c>
+      <c r="H109">
+        <v>9.380000000000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110">
+        <v>56</v>
+      </c>
+      <c r="B110">
+        <v>29</v>
+      </c>
+      <c r="C110">
+        <v>8</v>
+      </c>
+      <c r="D110">
+        <v>31.554916</v>
+      </c>
+      <c r="E110">
+        <v>75.184044</v>
+      </c>
+      <c r="F110">
+        <v>1.12</v>
+      </c>
+      <c r="G110">
+        <v>4.24</v>
+      </c>
+      <c r="H110">
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111">
+        <v>57</v>
+      </c>
+      <c r="B111">
+        <v>19</v>
+      </c>
+      <c r="C111">
+        <v>7</v>
+      </c>
+      <c r="D111">
+        <v>31.539066</v>
+      </c>
+      <c r="E111">
+        <v>75.244698</v>
+      </c>
+      <c r="F111">
+        <v>0.43</v>
+      </c>
+      <c r="G111">
+        <v>2.43</v>
+      </c>
+      <c r="H111">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112">
+        <v>57</v>
+      </c>
+      <c r="B112">
+        <v>20</v>
+      </c>
+      <c r="C112">
+        <v>7</v>
+      </c>
+      <c r="D112">
+        <v>31.539066</v>
+      </c>
+      <c r="E112">
+        <v>75.244698</v>
+      </c>
+      <c r="F112">
+        <v>0.43</v>
+      </c>
+      <c r="G112">
+        <v>2.84</v>
+      </c>
+      <c r="H112">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113">
+        <v>57</v>
+      </c>
+      <c r="B113">
+        <v>27</v>
+      </c>
+      <c r="C113">
+        <v>7</v>
+      </c>
+      <c r="D113">
+        <v>31.539066</v>
+      </c>
+      <c r="E113">
+        <v>75.244698</v>
+      </c>
+      <c r="F113">
+        <v>0.43</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114">
+        <v>57</v>
+      </c>
+      <c r="B114">
+        <v>28</v>
+      </c>
+      <c r="C114">
+        <v>7</v>
+      </c>
+      <c r="D114">
+        <v>31.539066</v>
+      </c>
+      <c r="E114">
+        <v>75.244698</v>
+      </c>
+      <c r="F114">
+        <v>0.43</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115">
+        <v>57</v>
+      </c>
+      <c r="B115">
+        <v>36</v>
+      </c>
+      <c r="C115">
+        <v>8</v>
+      </c>
+      <c r="D115">
+        <v>31.554916</v>
+      </c>
+      <c r="E115">
+        <v>75.184044</v>
+      </c>
+      <c r="F115">
+        <v>5.59</v>
+      </c>
+      <c r="G115">
+        <v>0.03</v>
+      </c>
+      <c r="H115">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116">
+        <v>57</v>
+      </c>
+      <c r="B116">
+        <v>37</v>
+      </c>
+      <c r="C116">
+        <v>8</v>
+      </c>
+      <c r="D116">
+        <v>31.554916</v>
+      </c>
+      <c r="E116">
+        <v>75.184044</v>
+      </c>
+      <c r="F116">
+        <v>5.59</v>
+      </c>
+      <c r="G116">
+        <v>0.03</v>
+      </c>
+      <c r="H116">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117">
+        <v>57</v>
+      </c>
+      <c r="B117">
+        <v>43</v>
+      </c>
+      <c r="C117">
+        <v>7</v>
+      </c>
+      <c r="D117">
+        <v>31.539066</v>
+      </c>
+      <c r="E117">
+        <v>75.244698</v>
+      </c>
+      <c r="F117">
+        <v>0.43</v>
+      </c>
+      <c r="G117">
+        <v>1.25</v>
+      </c>
+      <c r="H117">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118">
+        <v>58</v>
+      </c>
+      <c r="B118">
+        <v>17</v>
+      </c>
+      <c r="C118">
+        <v>7</v>
+      </c>
+      <c r="D118">
+        <v>31.539066</v>
+      </c>
+      <c r="E118">
+        <v>75.244698</v>
+      </c>
+      <c r="F118">
+        <v>5.5</v>
+      </c>
+      <c r="G118">
+        <v>2.63</v>
+      </c>
+      <c r="H118">
+        <v>8.119999999999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119">
+        <v>58</v>
+      </c>
+      <c r="B119">
+        <v>18</v>
+      </c>
+      <c r="C119">
+        <v>7</v>
+      </c>
+      <c r="D119">
+        <v>31.539066</v>
+      </c>
+      <c r="E119">
+        <v>75.244698</v>
+      </c>
+      <c r="F119">
+        <v>5.5</v>
+      </c>
+      <c r="G119">
+        <v>2.63</v>
+      </c>
+      <c r="H119">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120">
+        <v>58</v>
+      </c>
+      <c r="B120">
+        <v>35</v>
+      </c>
+      <c r="C120">
+        <v>8</v>
+      </c>
+      <c r="D120">
+        <v>31.554916</v>
+      </c>
+      <c r="E120">
+        <v>75.184044</v>
+      </c>
+      <c r="F120">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="G120">
+        <v>0.13</v>
+      </c>
+      <c r="H120">
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121">
+        <v>58</v>
+      </c>
+      <c r="B121">
+        <v>37</v>
+      </c>
+      <c r="C121">
+        <v>8</v>
+      </c>
+      <c r="D121">
+        <v>31.554916</v>
+      </c>
+      <c r="E121">
+        <v>75.184044</v>
+      </c>
+      <c r="F121">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="G121">
+        <v>0.03</v>
+      </c>
+      <c r="H121">
+        <v>9.82</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122">
+        <v>23</v>
+      </c>
+      <c r="B122">
+        <v>5</v>
+      </c>
+      <c r="C122">
+        <v>4</v>
+      </c>
+      <c r="D122">
+        <v>31.781936</v>
+      </c>
+      <c r="E122">
+        <v>74.76758049999999</v>
+      </c>
+      <c r="F122">
+        <v>15.86</v>
+      </c>
+      <c r="G122">
+        <v>17.05</v>
+      </c>
+      <c r="H122">
+        <v>32.91</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123">
+        <v>24</v>
+      </c>
+      <c r="B123">
+        <v>11</v>
+      </c>
+      <c r="C123">
+        <v>4</v>
+      </c>
+      <c r="D123">
+        <v>31.781936</v>
+      </c>
+      <c r="E123">
+        <v>74.76758049999999</v>
+      </c>
+      <c r="F123">
+        <v>13.57</v>
+      </c>
+      <c r="G123">
+        <v>11.56</v>
+      </c>
+      <c r="H123">
+        <v>25.13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124">
+        <v>24</v>
+      </c>
+      <c r="B124">
+        <v>12</v>
+      </c>
+      <c r="C124">
+        <v>4</v>
+      </c>
+      <c r="D124">
+        <v>31.781936</v>
+      </c>
+      <c r="E124">
+        <v>74.76758049999999</v>
+      </c>
+      <c r="F124">
+        <v>13.57</v>
+      </c>
+      <c r="G124">
+        <v>11.36</v>
+      </c>
+      <c r="H124">
+        <v>24.92</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125">
+        <v>36</v>
+      </c>
+      <c r="B125">
+        <v>13</v>
+      </c>
+      <c r="C125">
+        <v>10</v>
+      </c>
+      <c r="D125">
+        <v>31.571434</v>
+      </c>
+      <c r="E125">
+        <v>75.048013</v>
+      </c>
+      <c r="F125">
+        <v>0.53</v>
+      </c>
+      <c r="G125">
+        <v>4.37</v>
+      </c>
+      <c r="H125">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126">
+        <v>36</v>
+      </c>
+      <c r="B126">
+        <v>14</v>
+      </c>
+      <c r="C126">
+        <v>1899</v>
+      </c>
+      <c r="D126">
+        <v>31.51644</v>
+      </c>
+      <c r="E126">
+        <v>74.76897</v>
+      </c>
+      <c r="F126">
+        <v>26.62</v>
+      </c>
+      <c r="G126">
+        <v>29.63</v>
+      </c>
+      <c r="H126">
+        <v>56.25</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127">
+        <v>36</v>
+      </c>
+      <c r="B127">
+        <v>30</v>
+      </c>
+      <c r="C127">
+        <v>10</v>
+      </c>
+      <c r="D127">
+        <v>31.571434</v>
+      </c>
+      <c r="E127">
+        <v>75.048013</v>
+      </c>
+      <c r="F127">
+        <v>0.53</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128">
+        <v>36</v>
+      </c>
+      <c r="B128">
+        <v>31</v>
+      </c>
+      <c r="C128">
+        <v>10</v>
+      </c>
+      <c r="D128">
+        <v>31.571434</v>
+      </c>
+      <c r="E128">
+        <v>75.048013</v>
+      </c>
+      <c r="F128">
+        <v>0.53</v>
+      </c>
+      <c r="G128">
+        <v>1.35</v>
+      </c>
+      <c r="H128">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129">
+        <v>36</v>
+      </c>
+      <c r="B129">
+        <v>34</v>
+      </c>
+      <c r="C129">
+        <v>10</v>
+      </c>
+      <c r="D129">
+        <v>31.571434</v>
+      </c>
+      <c r="E129">
+        <v>75.048013</v>
+      </c>
+      <c r="F129">
+        <v>0.53</v>
+      </c>
+      <c r="G129">
+        <v>25.65</v>
+      </c>
+      <c r="H129">
+        <v>26.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130">
+        <v>38</v>
+      </c>
+      <c r="B130">
+        <v>13</v>
+      </c>
+      <c r="C130">
+        <v>484</v>
+      </c>
+      <c r="D130">
+        <v>31.594</v>
+      </c>
+      <c r="E130">
+        <v>75.09441</v>
+      </c>
+      <c r="F130">
+        <v>6.05</v>
+      </c>
+      <c r="G130">
+        <v>2.7</v>
+      </c>
+      <c r="H130">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131">
+        <v>40</v>
+      </c>
+      <c r="B131">
+        <v>13</v>
+      </c>
+      <c r="C131">
+        <v>484</v>
+      </c>
+      <c r="D131">
+        <v>31.594</v>
+      </c>
+      <c r="E131">
+        <v>75.09441</v>
+      </c>
+      <c r="F131">
+        <v>3.31</v>
+      </c>
+      <c r="G131">
+        <v>2.7</v>
+      </c>
+      <c r="H131">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132">
+        <v>1066</v>
+      </c>
+      <c r="B132">
+        <v>33</v>
+      </c>
+      <c r="C132">
+        <v>539</v>
+      </c>
+      <c r="D132">
+        <v>31.385438</v>
+      </c>
+      <c r="E132">
+        <v>75.536871</v>
+      </c>
+      <c r="F132">
+        <v>5.63</v>
+      </c>
+      <c r="G132">
+        <v>1.57</v>
+      </c>
+      <c r="H132">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133">
+        <v>10</v>
+      </c>
+      <c r="B133">
+        <v>41</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="D133">
+        <v>31.64602</v>
+      </c>
+      <c r="E133">
+        <v>74.85684000000001</v>
+      </c>
+      <c r="F133">
+        <v>4.85</v>
+      </c>
+      <c r="G133">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H133">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134">
+        <v>10</v>
+      </c>
+      <c r="B134">
+        <v>42</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134">
+        <v>31.64602</v>
+      </c>
+      <c r="E134">
+        <v>74.85684000000001</v>
+      </c>
+      <c r="F134">
+        <v>4.85</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135">
+        <v>10</v>
+      </c>
+      <c r="B135">
+        <v>6</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135">
+        <v>31.64602</v>
+      </c>
+      <c r="E135">
+        <v>74.85684000000001</v>
+      </c>
+      <c r="F135">
+        <v>4.85</v>
+      </c>
+      <c r="G135">
+        <v>9.52</v>
+      </c>
+      <c r="H135">
+        <v>14.37</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136">
+        <v>10</v>
+      </c>
+      <c r="B136">
+        <v>7</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136">
+        <v>31.64602</v>
+      </c>
+      <c r="E136">
+        <v>74.85684000000001</v>
+      </c>
+      <c r="F136">
+        <v>4.85</v>
+      </c>
+      <c r="G136">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H136">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137">
+        <v>10</v>
+      </c>
+      <c r="B137">
+        <v>8</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137">
+        <v>31.64602</v>
+      </c>
+      <c r="E137">
+        <v>74.85684000000001</v>
+      </c>
+      <c r="F137">
+        <v>4.85</v>
+      </c>
+      <c r="G137">
+        <v>7.67</v>
+      </c>
+      <c r="H137">
+        <v>12.52</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138">
+        <v>11</v>
+      </c>
+      <c r="B138">
+        <v>22</v>
+      </c>
+      <c r="C138">
+        <v>5</v>
+      </c>
+      <c r="D138">
+        <v>31.60898</v>
+      </c>
+      <c r="E138">
+        <v>74.78771999999999</v>
+      </c>
+      <c r="F138">
+        <v>2.78</v>
+      </c>
+      <c r="G138">
+        <v>5.71</v>
+      </c>
+      <c r="H138">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139">
+        <v>11</v>
+      </c>
+      <c r="B139">
+        <v>24</v>
+      </c>
+      <c r="C139">
+        <v>5</v>
+      </c>
+      <c r="D139">
+        <v>31.60898</v>
+      </c>
+      <c r="E139">
+        <v>74.78771999999999</v>
+      </c>
+      <c r="F139">
+        <v>2.78</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140">
+        <v>1660</v>
+      </c>
+      <c r="B140">
+        <v>407</v>
+      </c>
+      <c r="C140">
+        <v>287</v>
+      </c>
+      <c r="D140">
+        <v>30.126927</v>
+      </c>
+      <c r="E140">
+        <v>74.161942</v>
+      </c>
+      <c r="F140">
+        <v>17.93</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>17.93</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141">
+        <v>18</v>
+      </c>
+      <c r="B141">
+        <v>24</v>
+      </c>
+      <c r="C141">
+        <v>5</v>
+      </c>
+      <c r="D141">
+        <v>31.60898</v>
+      </c>
+      <c r="E141">
+        <v>74.78771999999999</v>
+      </c>
+      <c r="F141">
+        <v>4</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142">
+        <v>18</v>
+      </c>
+      <c r="B142">
+        <v>26</v>
+      </c>
+      <c r="C142">
+        <v>6</v>
+      </c>
+      <c r="D142">
+        <v>31.598156</v>
+      </c>
+      <c r="E142">
+        <v>74.784094</v>
+      </c>
+      <c r="F142">
+        <v>2.77</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143">
+        <v>2139</v>
+      </c>
+      <c r="B143">
+        <v>40</v>
+      </c>
+      <c r="C143">
+        <v>1934</v>
+      </c>
+      <c r="D143">
+        <v>31.404687</v>
+      </c>
+      <c r="E143">
+        <v>74.96226900000001</v>
+      </c>
+      <c r="F143">
+        <v>5.56</v>
+      </c>
+      <c r="G143">
+        <v>5.11</v>
+      </c>
+      <c r="H143">
+        <v>10.67</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144">
+        <v>2151</v>
+      </c>
+      <c r="B144">
+        <v>40</v>
+      </c>
+      <c r="C144">
+        <v>1906</v>
+      </c>
+      <c r="D144">
+        <v>31.465336</v>
+      </c>
+      <c r="E144">
+        <v>74.96441299999999</v>
+      </c>
+      <c r="F144">
+        <v>7.67</v>
+      </c>
+      <c r="G144">
+        <v>5.23</v>
+      </c>
+      <c r="H144">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145">
         <v>2153</v>
       </c>
-      <c r="B84">
+      <c r="B145">
+        <v>10</v>
+      </c>
+      <c r="C145">
+        <v>1948</v>
+      </c>
+      <c r="D145">
+        <v>31.361236</v>
+      </c>
+      <c r="E145">
+        <v>74.66727400000001</v>
+      </c>
+      <c r="F145">
+        <v>5.71</v>
+      </c>
+      <c r="G145">
+        <v>21.72</v>
+      </c>
+      <c r="H145">
+        <v>27.43</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146">
+        <v>2153</v>
+      </c>
+      <c r="B146">
         <v>4</v>
       </c>
-      <c r="C84">
+      <c r="C146">
         <v>1948</v>
       </c>
-      <c r="D84">
+      <c r="D146">
         <v>31.361236</v>
       </c>
-      <c r="E84">
+      <c r="E146">
         <v>74.66727400000001</v>
       </c>
-      <c r="F84">
+      <c r="F146">
         <v>5.71</v>
       </c>
-      <c r="G84">
+      <c r="G146">
         <v>21.72</v>
       </c>
-      <c r="H84">
+      <c r="H146">
         <v>27.43</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147">
+        <v>2153</v>
+      </c>
+      <c r="B147">
+        <v>9</v>
+      </c>
+      <c r="C147">
+        <v>1948</v>
+      </c>
+      <c r="D147">
+        <v>31.361236</v>
+      </c>
+      <c r="E147">
+        <v>74.66727400000001</v>
+      </c>
+      <c r="F147">
+        <v>5.71</v>
+      </c>
+      <c r="G147">
+        <v>21.72</v>
+      </c>
+      <c r="H147">
+        <v>27.43</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148">
+        <v>21</v>
+      </c>
+      <c r="B148">
+        <v>24</v>
+      </c>
+      <c r="C148">
+        <v>5</v>
+      </c>
+      <c r="D148">
+        <v>31.60898</v>
+      </c>
+      <c r="E148">
+        <v>74.78771999999999</v>
+      </c>
+      <c r="F148">
+        <v>5.28</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149">
+        <v>21</v>
+      </c>
+      <c r="B149">
+        <v>25</v>
+      </c>
+      <c r="C149">
+        <v>5</v>
+      </c>
+      <c r="D149">
+        <v>31.60898</v>
+      </c>
+      <c r="E149">
+        <v>74.78771999999999</v>
+      </c>
+      <c r="F149">
+        <v>5.28</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150">
+        <v>28</v>
+      </c>
+      <c r="B150">
+        <v>22</v>
+      </c>
+      <c r="C150">
+        <v>5</v>
+      </c>
+      <c r="D150">
+        <v>31.60898</v>
+      </c>
+      <c r="E150">
+        <v>74.78771999999999</v>
+      </c>
+      <c r="F150">
+        <v>9.99</v>
+      </c>
+      <c r="G150">
+        <v>5.71</v>
+      </c>
+      <c r="H150">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151">
+        <v>31</v>
+      </c>
+      <c r="B151">
+        <v>22</v>
+      </c>
+      <c r="C151">
+        <v>2</v>
+      </c>
+      <c r="D151">
+        <v>31.67995</v>
+      </c>
+      <c r="E151">
+        <v>74.84148999999999</v>
+      </c>
+      <c r="F151">
+        <v>6.19</v>
+      </c>
+      <c r="G151">
+        <v>5.54</v>
+      </c>
+      <c r="H151">
+        <v>11.74</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152">
+        <v>39</v>
+      </c>
+      <c r="B152">
+        <v>32</v>
+      </c>
+      <c r="C152">
+        <v>484</v>
+      </c>
+      <c r="D152">
+        <v>31.594</v>
+      </c>
+      <c r="E152">
+        <v>75.09441</v>
+      </c>
+      <c r="F152">
+        <v>6.02</v>
+      </c>
+      <c r="G152">
+        <v>7.96</v>
+      </c>
+      <c r="H152">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153">
+        <v>49</v>
+      </c>
+      <c r="B153">
+        <v>32</v>
+      </c>
+      <c r="C153">
+        <v>8</v>
+      </c>
+      <c r="D153">
+        <v>31.554916</v>
+      </c>
+      <c r="E153">
+        <v>75.184044</v>
+      </c>
+      <c r="F153">
+        <v>11.46</v>
+      </c>
+      <c r="G153">
+        <v>7.16</v>
+      </c>
+      <c r="H153">
+        <v>18.62</v>
       </c>
     </row>
   </sheetData>
